--- a/practice-files/day09-统计函数.xlsx
+++ b/practice-files/day09-统计函数.xlsx
@@ -8,8 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="练习说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销售记录" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销售记录" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -585,19 +584,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -650,20 +636,20 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>1726.43</v>
+        <v>659.95</v>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-01-02</t>
         </is>
       </c>
     </row>
@@ -680,15 +666,15 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1579.65</v>
+        <v>2966.8</v>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -700,20 +686,20 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>2705.38</v>
+        <v>1771.56</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-04-11</t>
         </is>
       </c>
     </row>
@@ -725,20 +711,20 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1247.64</v>
+        <v>38.42</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
@@ -750,7 +736,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -759,11 +745,11 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>1990.76</v>
+        <v>2401.59</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-02-22</t>
         </is>
       </c>
     </row>
@@ -775,20 +761,20 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>588.33</v>
+        <v>74.14</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-19</t>
         </is>
       </c>
     </row>
@@ -800,20 +786,20 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>2189.5</v>
+        <v>547.51</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-01-05</t>
         </is>
       </c>
     </row>
@@ -825,7 +811,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -834,11 +820,11 @@
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2664.46</v>
+        <v>367.54</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-02-16</t>
         </is>
       </c>
     </row>
@@ -850,7 +836,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -859,11 +845,11 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>42.5</v>
+        <v>1554.32</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-02-15</t>
         </is>
       </c>
     </row>
@@ -875,20 +861,20 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2524.14</v>
+        <v>2837.88</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-01-24</t>
         </is>
       </c>
     </row>
@@ -900,20 +886,20 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1963.25</v>
+        <v>1390.39</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-02</t>
         </is>
       </c>
     </row>
@@ -925,20 +911,20 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1095.09</v>
+        <v>1296.03</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-02-16</t>
         </is>
       </c>
     </row>
@@ -955,15 +941,15 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>2350.35</v>
+        <v>2700.82</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -980,15 +966,15 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>629.84</v>
+        <v>404.79</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -1000,7 +986,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -1009,11 +995,11 @@
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>2998.03</v>
+        <v>905.85</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -1025,20 +1011,20 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2755.68</v>
+        <v>1963.22</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-04-14</t>
         </is>
       </c>
     </row>
@@ -1055,15 +1041,15 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>803.23</v>
+        <v>1259.03</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1075,20 +1061,20 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1568.53</v>
+        <v>312.4</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -1105,15 +1091,15 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>2058.7</v>
+        <v>2862.17</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -1130,15 +1116,15 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2158.29</v>
+        <v>306.89</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-24</t>
         </is>
       </c>
     </row>
@@ -1150,20 +1136,20 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>1560.43</v>
+        <v>1682.42</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
@@ -1175,20 +1161,20 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2297.04</v>
+        <v>1080.19</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -1200,20 +1186,20 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>2271.69</v>
+        <v>1813.22</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -1225,20 +1211,20 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>773.3099999999999</v>
+        <v>661.83</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -1250,20 +1236,20 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>2029.15</v>
+        <v>2540.76</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -1275,20 +1261,20 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>385.11</v>
+        <v>701.6900000000001</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -1300,20 +1286,20 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>1950.71</v>
+        <v>1852.31</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-20</t>
         </is>
       </c>
     </row>
@@ -1325,20 +1311,20 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>49.88</v>
+        <v>565.84</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1350,20 +1336,20 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>1253.99</v>
+        <v>568.77</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-03-19</t>
         </is>
       </c>
     </row>
@@ -1375,20 +1361,20 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>218.06</v>
+        <v>451.37</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-03</t>
         </is>
       </c>
     </row>
@@ -1400,20 +1386,20 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>2443.33</v>
+        <v>1147.3</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -1425,20 +1411,20 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>1205.15</v>
+        <v>955.5599999999999</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1436,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -1459,11 +1445,11 @@
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>1057.86</v>
+        <v>282.32</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-01-05</t>
         </is>
       </c>
     </row>
@@ -1480,15 +1466,15 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>1503.22</v>
+        <v>177.79</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-09</t>
         </is>
       </c>
     </row>
@@ -1500,20 +1486,20 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>2006.86</v>
+        <v>1289.32</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -1525,20 +1511,20 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>1179.55</v>
+        <v>2272.18</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-02-12</t>
         </is>
       </c>
     </row>
@@ -1550,20 +1536,20 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>966.05</v>
+        <v>871.24</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -1575,20 +1561,20 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>197.01</v>
+        <v>684.9400000000001</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-01</t>
         </is>
       </c>
     </row>
@@ -1609,11 +1595,11 @@
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>1584.63</v>
+        <v>2837.61</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-03-25</t>
         </is>
       </c>
     </row>
@@ -1625,20 +1611,20 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>2647.25</v>
+        <v>1004.52</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-01-16</t>
         </is>
       </c>
     </row>

--- a/practice-files/day09-统计函数.xlsx
+++ b/practice-files/day09-统计函数.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +33,22 @@
     </font>
     <font>
       <name val="微软雅黑"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00E67E22"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="002E7D32"/>
       <sz val="10.5"/>
     </font>
     <font>
@@ -91,17 +107,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -467,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -569,7 +590,49 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>【思考】哪个分类的平均客单价最高？用AVERAGEIF试试。</t>
+          <t>【思考】哪个分类的平均客单价最高？用AVERAGEIF试试。（答案见下方折叠区）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>📝 思考题（先自己想想，点左侧+号展开答案）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>思考题1: COUNT和COUNTA混用会有什么后果？</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" hidden="1" outlineLevel="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>💡 答案: COUNT只数数字，COUNTA数所有非空。给"用户名"这种文本列用COUNT会得到0，人数统计全错。统计前先想清楚列的类型。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>思考题2: 用AVERAGEIF算一下：本数据里哪个分类的平均客单价最高？</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" hidden="1" outlineLevel="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>💡 答案: 答案是"电子产品"（平均1562.72元/单）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" hidden="1" outlineLevel="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>方法：=AVERAGEIF(分类列,某分类,金额列)，每个分类各算一遍再比较。</t>
         </is>
       </c>
     </row>
@@ -597,1032 +660,1032 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>订单ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>分类</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>城市</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>← 在这里写公式练习</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>ORD-0001</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>成都</t>
         </is>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="8" t="n">
         <v>659.95</v>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>2026-01-02</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>ORD-0002</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>食品饮料</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="8" t="n">
         <v>2966.8</v>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>ORD-0003</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>运动户外</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="8" t="n">
         <v>1771.56</v>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>2026-04-11</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>ORD-0004</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>服装鞋帽</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>杭州</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="8" t="n">
         <v>38.42</v>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>ORD-0005</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>运动户外</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>广州</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="8" t="n">
         <v>2401.59</v>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>2026-02-22</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>ORD-0006</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="8" t="n">
         <v>74.14</v>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>2026-04-19</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>ORD-0007</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>食品饮料</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="8" t="n">
         <v>547.51</v>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>2026-01-05</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>ORD-0008</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>家居用品</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>杭州</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="8" t="n">
         <v>367.54</v>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>ORD-0009</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>家居用品</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>广州</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="8" t="n">
         <v>1554.32</v>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>2026-02-15</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>ORD-0010</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>运动户外</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="8" t="n">
         <v>2837.88</v>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>ORD-0011</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>运动户外</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>广州</t>
         </is>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="8" t="n">
         <v>1390.39</v>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>2026-01-02</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>ORD-0012</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>家居用品</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>深圳</t>
         </is>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="8" t="n">
         <v>1296.03</v>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>ORD-0013</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>家居用品</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="8" t="n">
         <v>2700.82</v>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>ORD-0014</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>服装鞋帽</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="8" t="n">
         <v>404.79</v>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>ORD-0015</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>运动户外</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>杭州</t>
         </is>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D16" s="8" t="n">
         <v>905.85</v>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>ORD-0016</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>成都</t>
         </is>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D17" s="8" t="n">
         <v>1963.22</v>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>ORD-0017</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>家居用品</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D18" s="8" t="n">
         <v>1259.03</v>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>ORD-0018</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>家居用品</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>成都</t>
         </is>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D19" s="8" t="n">
         <v>312.4</v>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>ORD-0019</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>食品饮料</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>广州</t>
         </is>
       </c>
-      <c r="D20" s="5" t="n">
+      <c r="D20" s="8" t="n">
         <v>2862.17</v>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>ORD-0020</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D21" s="8" t="n">
         <v>306.89</v>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>2026-02-24</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>ORD-0021</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>食品饮料</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
-      <c r="D22" s="5" t="n">
+      <c r="D22" s="8" t="n">
         <v>1682.42</v>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>ORD-0022</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>深圳</t>
         </is>
       </c>
-      <c r="D23" s="5" t="n">
+      <c r="D23" s="8" t="n">
         <v>1080.19</v>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>ORD-0023</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>广州</t>
         </is>
       </c>
-      <c r="D24" s="5" t="n">
+      <c r="D24" s="8" t="n">
         <v>1813.22</v>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>ORD-0024</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>运动户外</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>杭州</t>
         </is>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="D25" s="8" t="n">
         <v>661.83</v>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>ORD-0025</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>广州</t>
         </is>
       </c>
-      <c r="D26" s="5" t="n">
+      <c r="D26" s="8" t="n">
         <v>2540.76</v>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>ORD-0026</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>食品饮料</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>杭州</t>
         </is>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D27" s="8" t="n">
         <v>701.6900000000001</v>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>ORD-0027</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>运动户外</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>杭州</t>
         </is>
       </c>
-      <c r="D28" s="5" t="n">
+      <c r="D28" s="8" t="n">
         <v>1852.31</v>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>2026-01-20</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>ORD-0028</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>食品饮料</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="D29" s="5" t="n">
+      <c r="D29" s="8" t="n">
         <v>565.84</v>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>ORD-0029</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>食品饮料</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="D30" s="5" t="n">
+      <c r="D30" s="8" t="n">
         <v>568.77</v>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>ORD-0030</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>家居用品</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="D31" s="5" t="n">
+      <c r="D31" s="8" t="n">
         <v>451.37</v>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>2026-01-03</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>ORD-0031</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>运动户外</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
-      <c r="D32" s="5" t="n">
+      <c r="D32" s="8" t="n">
         <v>1147.3</v>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>ORD-0032</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>服装鞋帽</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>广州</t>
         </is>
       </c>
-      <c r="D33" s="5" t="n">
+      <c r="D33" s="8" t="n">
         <v>955.5599999999999</v>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>ORD-0033</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>运动户外</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>杭州</t>
         </is>
       </c>
-      <c r="D34" s="5" t="n">
+      <c r="D34" s="8" t="n">
         <v>282.32</v>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>2026-01-05</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>ORD-0034</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>服装鞋帽</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>杭州</t>
         </is>
       </c>
-      <c r="D35" s="5" t="n">
+      <c r="D35" s="8" t="n">
         <v>177.79</v>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>ORD-0035</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>家居用品</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>成都</t>
         </is>
       </c>
-      <c r="D36" s="5" t="n">
+      <c r="D36" s="8" t="n">
         <v>1289.32</v>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>ORD-0036</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>食品饮料</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
-      <c r="D37" s="5" t="n">
+      <c r="D37" s="8" t="n">
         <v>2272.18</v>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>2026-02-12</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>ORD-0037</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>家居用品</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="D38" s="5" t="n">
+      <c r="D38" s="8" t="n">
         <v>871.24</v>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>ORD-0038</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>食品饮料</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="D39" s="5" t="n">
+      <c r="D39" s="8" t="n">
         <v>684.9400000000001</v>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>ORD-0039</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>服装鞋帽</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>广州</t>
         </is>
       </c>
-      <c r="D40" s="5" t="n">
+      <c r="D40" s="8" t="n">
         <v>2837.61</v>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E40" s="8" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>ORD-0040</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>食品饮料</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>广州</t>
         </is>
       </c>
-      <c r="D41" s="5" t="n">
+      <c r="D41" s="8" t="n">
         <v>1004.52</v>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>2026-01-16</t>
         </is>

--- a/practice-files/day09-统计函数.xlsx
+++ b/practice-files/day09-统计函数.xlsx
@@ -597,7 +597,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>📝 思考题（先自己想想，点左侧+号展开答案）</t>
+          <t>思考题（先自己想想，点左侧+号展开答案）</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
     <row r="21" hidden="1" outlineLevel="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>💡 答案: COUNT只数数字，COUNTA数所有非空。给"用户名"这种文本列用COUNT会得到0，人数统计全错。统计前先想清楚列的类型。</t>
+          <t>答案: COUNT只数数字，COUNTA数所有非空。给"用户名"这种文本列用COUNT会得到0，人数统计全错。统计前先想清楚列的类型。</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
     <row r="24" hidden="1" outlineLevel="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>💡 答案: 答案是"电子产品"（平均1562.72元/单）。</t>
+          <t>答案: 答案是"电子产品"（平均1562.72元/单）。</t>
         </is>
       </c>
     </row>

--- a/practice-files/day09-统计函数.xlsx
+++ b/practice-files/day09-统计函数.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="练习说明" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销售记录" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="靓号库(备用实战)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -488,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -585,52 +586,59 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>【备用实战】"靓号库(备用实战)"工作表模拟靓号库，练COUNTIF统计规律类型用</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>【思考】哪个分类的平均客单价最高？用AVERAGEIF试试。（答案见下方折叠区）</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>思考题（先自己想想，点左侧+号展开答案）</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>思考题1: COUNT和COUNTA混用会有什么后果？</t>
         </is>
       </c>
     </row>
-    <row r="21" hidden="1" outlineLevel="1">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="22" hidden="1" outlineLevel="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>答案: COUNT只数数字，COUNTA数所有非空。给"用户名"这种文本列用COUNT会得到0，人数统计全错。统计前先想清楚列的类型。</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>思考题2: 用AVERAGEIF算一下：本数据里哪个分类的平均客单价最高？</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" hidden="1" outlineLevel="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>答案: 答案是"电子产品"（平均1562.72元/单）。</t>
         </is>
       </c>
     </row>
     <row r="25" hidden="1" outlineLevel="1">
       <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>答案: 答案是"电子产品"（平均1562.72元/单）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" hidden="1" outlineLevel="1">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>方法：=AVERAGEIF(分类列,某分类,金额列)，每个分类各算一遍再比较。</t>
         </is>
@@ -699,20 +707,20 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D2" s="8" t="n">
-        <v>659.95</v>
+        <v>2404.52</v>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-03-12</t>
         </is>
       </c>
     </row>
@@ -733,11 +741,11 @@
         </is>
       </c>
       <c r="D3" s="8" t="n">
-        <v>2966.8</v>
+        <v>1388.92</v>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
@@ -749,20 +757,20 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>1771.56</v>
+        <v>2898.77</v>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -774,7 +782,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -783,11 +791,11 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>38.42</v>
+        <v>1195.86</v>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-12</t>
         </is>
       </c>
     </row>
@@ -799,20 +807,20 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>2401.59</v>
+        <v>1863.57</v>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
@@ -824,20 +832,20 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>74.14</v>
+        <v>2026.17</v>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -849,20 +857,20 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>547.51</v>
+        <v>377.34</v>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-06-23</t>
         </is>
       </c>
     </row>
@@ -874,7 +882,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -883,11 +891,11 @@
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>367.54</v>
+        <v>1183.74</v>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
     </row>
@@ -904,15 +912,15 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>1554.32</v>
+        <v>581.6900000000001</v>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -924,20 +932,20 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>2837.88</v>
+        <v>887.84</v>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-03-11</t>
         </is>
       </c>
     </row>
@@ -949,20 +957,20 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>1390.39</v>
+        <v>189.23</v>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -979,15 +987,15 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>1296.03</v>
+        <v>609.53</v>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -999,20 +1007,20 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2700.82</v>
+        <v>1500.06</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -1024,20 +1032,20 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>404.79</v>
+        <v>526.74</v>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-01-26</t>
         </is>
       </c>
     </row>
@@ -1049,20 +1057,20 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>905.85</v>
+        <v>127.1</v>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-04-18</t>
         </is>
       </c>
     </row>
@@ -1074,20 +1082,20 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>1963.22</v>
+        <v>2348.8</v>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -1099,20 +1107,20 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1259.03</v>
+        <v>1730.96</v>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1124,20 +1132,20 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>312.4</v>
+        <v>1639.87</v>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-01-25</t>
         </is>
       </c>
     </row>
@@ -1149,20 +1157,20 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2862.17</v>
+        <v>679.0700000000001</v>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -1174,20 +1182,20 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>306.89</v>
+        <v>2628.19</v>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-15</t>
         </is>
       </c>
     </row>
@@ -1204,15 +1212,15 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>1682.42</v>
+        <v>2590.73</v>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-02-15</t>
         </is>
       </c>
     </row>
@@ -1229,15 +1237,15 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>1080.19</v>
+        <v>653.34</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-28</t>
         </is>
       </c>
     </row>
@@ -1249,20 +1257,20 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>1813.22</v>
+        <v>1301.66</v>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -1274,20 +1282,20 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>661.83</v>
+        <v>2422.16</v>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
     </row>
@@ -1299,20 +1307,20 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>2540.76</v>
+        <v>1630.14</v>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-23</t>
         </is>
       </c>
     </row>
@@ -1329,15 +1337,15 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>701.6900000000001</v>
+        <v>1731.02</v>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-02-05</t>
         </is>
       </c>
     </row>
@@ -1349,20 +1357,20 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>1852.31</v>
+        <v>2977.68</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1374,20 +1382,20 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D29" s="8" t="n">
-        <v>565.84</v>
+        <v>464.34</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -1399,16 +1407,16 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>568.77</v>
+        <v>1196.32</v>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
@@ -1424,20 +1432,20 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>451.37</v>
+        <v>1260.25</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -1449,20 +1457,20 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>1147.3</v>
+        <v>1561.37</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -1474,20 +1482,20 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>955.5599999999999</v>
+        <v>2852.25</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
@@ -1499,20 +1507,20 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>282.32</v>
+        <v>306.63</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -1524,20 +1532,20 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>177.79</v>
+        <v>2393.16</v>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
@@ -1554,15 +1562,15 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>1289.32</v>
+        <v>1499.3</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -1579,15 +1587,15 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>2272.18</v>
+        <v>1655.51</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-19</t>
         </is>
       </c>
     </row>
@@ -1604,15 +1612,15 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>871.24</v>
+        <v>2685.64</v>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-01-02</t>
         </is>
       </c>
     </row>
@@ -1624,20 +1632,20 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>684.9400000000001</v>
+        <v>2358.15</v>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -1649,20 +1657,20 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D40" s="8" t="n">
-        <v>2837.61</v>
+        <v>1340.62</v>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-01-14</t>
         </is>
       </c>
     </row>
@@ -1674,20 +1682,1908 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D41" s="8" t="n">
-        <v>1004.52</v>
+        <v>2730.94</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E81"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>号码</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>位数</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>规律类型</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>价格(乐元)</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>上架状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>5415888</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>158</v>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>10371293</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>136</v>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>6271361</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>108</v>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>2218888</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>135</v>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>973112</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>147</v>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>23419999</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>豹子</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>96</v>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>9833456</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>顺子</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>05526</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>362</v>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>109104</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>下架</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>86661889</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>285691</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>71</v>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>下架</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>161888</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>202888</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>166</v>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>4105888</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>85079</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>80123</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>顺子</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>63536</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>283</v>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>0238888</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>457</v>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>8704444</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>豹子</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>119</v>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>38320603</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>151</v>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>06413</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>119</v>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>24103</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>347</v>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>1918261</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>105</v>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>452345</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>顺子</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>96</v>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>27888</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>41125555</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>豹子</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>下架</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>44206788</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>032888</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>1013721</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>446</v>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>02966</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>2444567</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>顺子</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>152</v>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>46263888</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>179</v>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>7598564</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>66</v>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>7859888</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>39652</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>79</v>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>0599293</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>165</v>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>下架</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>0103888</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>下架</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>525002</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>173</v>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>5691545</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>下架</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>28953926</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>84</v>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>96902</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>174</v>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>下架</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>172513</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>66</v>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>57043</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>53</v>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>06762</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>338</v>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>79327888</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>6218888</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>466</v>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>29620153</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>312</v>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>4310698</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>112</v>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>97310888</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>332</v>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>41862565</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>4906789</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>顺子</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="n">
+        <v>178</v>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>86879</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>333</v>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>89921</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="n">
+        <v>324</v>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>下架</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>320616</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>1164444</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>豹子</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="n">
+        <v>173</v>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>22999888</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>163</v>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>4679970</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>53074888</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>124</v>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>13247546</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="n">
+        <v>107</v>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>85082148</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>88</v>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>30888</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>8610357</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>114</v>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>4149933</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>AABB</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="n">
+        <v>388</v>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>8007229</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="n">
+        <v>118</v>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>4665743</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="n">
+        <v>83</v>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>08589944</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="n">
+        <v>139</v>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>4443283</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="n">
+        <v>438</v>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>20744666</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="n">
+        <v>147</v>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>下架</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>382288</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>AABB</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>8251353</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="n">
+        <v>125</v>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>9479999</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>AABB</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>60223569</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="n">
+        <v>496</v>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>752500</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>129666</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>058300</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>1680000</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>豹子</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>2570033</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>AABB</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>21506</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="n">
+        <v>263</v>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>01001</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>30461849</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="n">
+        <v>111</v>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>已售</t>
         </is>
       </c>
     </row>

--- a/practice-files/day09-统计函数.xlsx
+++ b/practice-files/day09-统计函数.xlsx
@@ -588,7 +588,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>【备用实战】"靓号库(备用实战)"工作表模拟靓号库，练COUNTIF统计规律类型用</t>
+          <t>【备用实战】"靓号库(备用实战)"工作表模拟靓号库，练COUNTIF统计类别(规律类型)用</t>
         </is>
       </c>
     </row>
@@ -707,20 +707,20 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="D2" s="8" t="n">
-        <v>2404.52</v>
+        <v>1372.42</v>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
     </row>
@@ -732,20 +732,20 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D3" s="8" t="n">
-        <v>1388.92</v>
+        <v>856.33</v>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -762,15 +762,15 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>2898.77</v>
+        <v>1758.41</v>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-02-24</t>
         </is>
       </c>
     </row>
@@ -787,15 +787,15 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>1195.86</v>
+        <v>2002.51</v>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-06-28</t>
         </is>
       </c>
     </row>
@@ -807,20 +807,20 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>1863.57</v>
+        <v>1211.22</v>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -832,20 +832,20 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>2026.17</v>
+        <v>827.55</v>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -857,20 +857,20 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>377.34</v>
+        <v>417.86</v>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -882,20 +882,20 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>1183.74</v>
+        <v>2293.89</v>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-01-04</t>
         </is>
       </c>
     </row>
@@ -912,15 +912,15 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>581.6900000000001</v>
+        <v>398.98</v>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-15</t>
         </is>
       </c>
     </row>
@@ -932,20 +932,20 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>887.84</v>
+        <v>2975.76</v>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
@@ -957,20 +957,20 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>189.23</v>
+        <v>926.54</v>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -982,20 +982,20 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>609.53</v>
+        <v>274.79</v>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1016,11 +1016,11 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>1500.06</v>
+        <v>937.36</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-04-14</t>
         </is>
       </c>
     </row>
@@ -1032,20 +1032,20 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>526.74</v>
+        <v>312.7</v>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
@@ -1057,20 +1057,20 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>127.1</v>
+        <v>1793.23</v>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -1082,20 +1082,20 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>2348.8</v>
+        <v>1050.42</v>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-02-28</t>
         </is>
       </c>
     </row>
@@ -1107,20 +1107,20 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1730.96</v>
+        <v>422.56</v>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-02-08</t>
         </is>
       </c>
     </row>
@@ -1132,20 +1132,20 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>1639.87</v>
+        <v>2200.37</v>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-02-04</t>
         </is>
       </c>
     </row>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>679.0700000000001</v>
+        <v>2646.54</v>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-03-13</t>
         </is>
       </c>
     </row>
@@ -1187,15 +1187,15 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>2628.19</v>
+        <v>2979.03</v>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-03-03</t>
         </is>
       </c>
     </row>
@@ -1207,20 +1207,20 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>2590.73</v>
+        <v>55.17</v>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-03-15</t>
         </is>
       </c>
     </row>
@@ -1232,20 +1232,20 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>653.34</v>
+        <v>662.77</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-03-14</t>
         </is>
       </c>
     </row>
@@ -1266,11 +1266,11 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>1301.66</v>
+        <v>1343.88</v>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -1291,11 +1291,11 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>2422.16</v>
+        <v>2264.76</v>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
     </row>
@@ -1307,20 +1307,20 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>1630.14</v>
+        <v>2379.5</v>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -1332,20 +1332,20 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>1731.02</v>
+        <v>1673.59</v>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1357,20 +1357,20 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>2977.68</v>
+        <v>2631.21</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1382,20 +1382,20 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="D29" s="8" t="n">
-        <v>464.34</v>
+        <v>590.28</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
@@ -1407,20 +1407,20 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>1196.32</v>
+        <v>1499.82</v>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-02-08</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -1441,11 +1441,11 @@
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>1260.25</v>
+        <v>1793.97</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-01-12</t>
         </is>
       </c>
     </row>
@@ -1457,20 +1457,20 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>1561.37</v>
+        <v>1178.91</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-07-12</t>
         </is>
       </c>
     </row>
@@ -1482,20 +1482,20 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>2852.25</v>
+        <v>543.13</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
@@ -1512,15 +1512,15 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>306.63</v>
+        <v>1774.47</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-01-09</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -1541,11 +1541,11 @@
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>2393.16</v>
+        <v>2770.06</v>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
@@ -1557,20 +1557,20 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>1499.3</v>
+        <v>2146.51</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -1582,20 +1582,20 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>1655.51</v>
+        <v>1932.4</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -1616,11 +1616,11 @@
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>2685.64</v>
+        <v>264.69</v>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1632,20 +1632,20 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>2358.15</v>
+        <v>1000.45</v>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-02-10</t>
         </is>
       </c>
     </row>
@@ -1657,20 +1657,20 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D40" s="8" t="n">
-        <v>1340.62</v>
+        <v>2861.68</v>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -1687,15 +1687,15 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D41" s="8" t="n">
-        <v>2730.94</v>
+        <v>2776.14</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-15</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1718,12 +1718,13 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>号码</t>
+          <t>靓号ID</t>
         </is>
       </c>
       <c r="B1" s="6" t="inlineStr">
@@ -1733,7 +1734,7 @@
       </c>
       <c r="C1" s="6" t="inlineStr">
         <is>
-          <t>规律类型</t>
+          <t>类别</t>
         </is>
       </c>
       <c r="D1" s="6" t="inlineStr">
@@ -1743,64 +1744,79 @@
       </c>
       <c r="E1" s="6" t="inlineStr">
         <is>
-          <t>上架状态</t>
+          <t>购买方式</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>赠送VIP</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>5415888</t>
+          <t>32222</t>
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>豹子</t>
         </is>
       </c>
       <c r="D2" s="8" t="n">
-        <v>158</v>
+        <v>67</v>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>10371293</t>
+          <t>3410888</t>
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="D3" s="8" t="n">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>VIP 6个月</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>6271361</t>
+          <t>17925241</t>
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
@@ -1808,22 +1824,27 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>108</v>
+        <v>396</v>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>2218888</t>
+          <t>13888</t>
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
@@ -1831,18 +1852,23 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>135</v>
+        <v>57</v>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>VIP 6个月</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>973112</t>
+          <t>751111</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
@@ -1850,45 +1876,55 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>豹子</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>23419999</t>
+          <t>27445</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>豹子</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>9833456</t>
+          <t>5937597</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
@@ -1896,22 +1932,27 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>顺子</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>62</v>
+        <v>429</v>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>VIP 1个月</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>05526</t>
+          <t>13850</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
@@ -1923,18 +1964,23 @@
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>362</v>
+        <v>181</v>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>109104</t>
+          <t>467024</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
@@ -1946,18 +1992,23 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>下架</t>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>VIP 3个月</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>86661889</t>
+          <t>29182619</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
@@ -1969,22 +2020,27 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>54</v>
+        <v>135</v>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>VIP 3个月</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>285691</t>
+          <t>7557431</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
@@ -1992,22 +2048,27 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>71</v>
+        <v>224</v>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>下架</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>VIP 1个月</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>161888</t>
+          <t>85888</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
@@ -2015,64 +2076,79 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>202888</t>
+          <t>21241234</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>顺子</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>4105888</t>
+          <t>52067</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>38</v>
+        <v>144</v>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>85079</t>
+          <t>31003</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
@@ -2084,18 +2160,23 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>80123</t>
+          <t>51013</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
@@ -2103,95 +2184,115 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>顺子</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>69</v>
+        <v>322</v>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>63536</t>
+          <t>8029888</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>283</v>
+        <v>37</v>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>0238888</t>
+          <t>547209</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>457</v>
+        <v>120</v>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>8704444</t>
+          <t>80146263</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>豹子</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>38320603</t>
+          <t>67875</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
@@ -2199,156 +2300,191 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>151</v>
+        <v>341</v>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>06413</t>
+          <t>404888</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>24103</t>
+          <t>448888</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>347</v>
+        <v>164</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>1918261</t>
+          <t>659888</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>452345</t>
+          <t>37010393</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>顺子</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>27888</t>
+          <t>625002</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>24</v>
+        <v>173</v>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>41125555</t>
+          <t>7915452</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>豹子</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>38</v>
+        <v>415</v>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>下架</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>44206788</t>
+          <t>38953926</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
@@ -2360,45 +2496,55 @@
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>032888</t>
+          <t>79029</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D29" s="8" t="n">
-        <v>175</v>
+        <v>90</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>1013721</t>
+          <t>35135</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
@@ -2406,68 +2552,83 @@
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>446</v>
+        <v>235</v>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>VIP 3个月</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>02966</t>
+          <t>43154888</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>VIP 6个月</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>2444567</t>
+          <t>71790044</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>顺子</t>
+          <t>AABB</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>152</v>
+        <v>20</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>46263888</t>
+          <t>7218888</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
@@ -2475,64 +2636,79 @@
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>179</v>
+        <v>466</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>VIP 1个月</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>7598564</t>
+          <t>25336888</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>7859888</t>
+          <t>82050614</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>62</v>
+        <v>150</v>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>39652</t>
+          <t>34888</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
@@ -2540,22 +2716,27 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>0599293</t>
+          <t>9625888</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
@@ -2563,49 +2744,59 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>165</v>
+        <v>63</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>下架</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>0103888</t>
+          <t>121158</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>下架</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>525002</t>
+          <t>96879</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
@@ -2613,22 +2804,27 @@
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>173</v>
+        <v>333</v>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>5691545</t>
+          <t>99921</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
@@ -2636,45 +2832,55 @@
         </is>
       </c>
       <c r="D40" s="8" t="n">
-        <v>16</v>
+        <v>324</v>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>下架</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>VIP 1个月</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>28953926</t>
+          <t>716888</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="D41" s="8" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>96902</t>
+          <t>95487099</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
@@ -2682,18 +2888,23 @@
         </is>
       </c>
       <c r="D42" s="8" t="n">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>下架</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>172513</t>
+          <t>219148</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
@@ -2705,22 +2916,27 @@
         </is>
       </c>
       <c r="D43" s="8" t="n">
-        <v>66</v>
+        <v>461</v>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>57043</t>
+          <t>80246299</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
@@ -2728,22 +2944,27 @@
         </is>
       </c>
       <c r="D44" s="8" t="n">
-        <v>53</v>
+        <v>132</v>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>06762</t>
+          <t>1745054</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
@@ -2751,68 +2972,83 @@
         </is>
       </c>
       <c r="D45" s="8" t="n">
-        <v>338</v>
+        <v>91</v>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>VIP 1个月</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>79327888</t>
+          <t>853333</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>豹子</t>
         </is>
       </c>
       <c r="D46" s="8" t="n">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>6218888</t>
+          <t>60821486</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D47" s="8" t="n">
-        <v>466</v>
+        <v>43</v>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>VIP 1个月</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>29620153</t>
+          <t>403070</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
@@ -2820,22 +3056,27 @@
         </is>
       </c>
       <c r="D48" s="8" t="n">
-        <v>312</v>
+        <v>406</v>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>4310698</t>
+          <t>20357972</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
@@ -2843,22 +3084,27 @@
         </is>
       </c>
       <c r="D49" s="8" t="n">
-        <v>112</v>
+        <v>332</v>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>97310888</t>
+          <t>5140888</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
@@ -2866,22 +3112,27 @@
         </is>
       </c>
       <c r="D50" s="8" t="n">
-        <v>332</v>
+        <v>430</v>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>41862565</t>
+          <t>446800</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
@@ -2889,22 +3140,27 @@
         </is>
       </c>
       <c r="D51" s="8" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>4906789</t>
+          <t>53456</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
@@ -2912,18 +3168,23 @@
         </is>
       </c>
       <c r="D52" s="8" t="n">
-        <v>178</v>
+        <v>73</v>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>86879</t>
+          <t>68994</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
@@ -2935,22 +3196,27 @@
         </is>
       </c>
       <c r="D53" s="8" t="n">
-        <v>333</v>
+        <v>55</v>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>89921</t>
+          <t>5443283</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
@@ -2958,18 +3224,23 @@
         </is>
       </c>
       <c r="D54" s="8" t="n">
-        <v>324</v>
+        <v>438</v>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>下架</t>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>VIP 3个月</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>320616</t>
+          <t>844666</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
@@ -2981,64 +3252,79 @@
         </is>
       </c>
       <c r="D55" s="8" t="n">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>VIP 3个月</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>1164444</t>
+          <t>858428</t>
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>豹子</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D56" s="8" t="n">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>22999888</t>
+          <t>9251353</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D57" s="8" t="n">
-        <v>163</v>
+        <v>125</v>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>VIP 3个月</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>4679970</t>
+          <t>8170999</t>
         </is>
       </c>
       <c r="B58" s="8" t="n">
@@ -3050,18 +3336,23 @@
         </is>
       </c>
       <c r="D58" s="8" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>53074888</t>
+          <t>70223569</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
@@ -3069,26 +3360,31 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D59" s="8" t="n">
-        <v>124</v>
+        <v>496</v>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>13247546</t>
+          <t>852500</t>
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
@@ -3096,68 +3392,83 @@
         </is>
       </c>
       <c r="D60" s="8" t="n">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>VIP 6个月</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>85082148</t>
+          <t>76888</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="D61" s="8" t="n">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>30888</t>
+          <t>6830033</t>
         </is>
       </c>
       <c r="B62" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D62" s="8" t="n">
-        <v>24</v>
+        <v>128</v>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>8610357</t>
+          <t>52104478</t>
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
@@ -3165,22 +3476,27 @@
         </is>
       </c>
       <c r="D63" s="8" t="n">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>VIP 3个月</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>4149933</t>
+          <t>42600099</t>
         </is>
       </c>
       <c r="B64" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
@@ -3188,18 +3504,23 @@
         </is>
       </c>
       <c r="D64" s="8" t="n">
-        <v>388</v>
+        <v>110</v>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>VIP 6个月</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>8007229</t>
+          <t>1901001</t>
         </is>
       </c>
       <c r="B65" s="8" t="n">
@@ -3211,22 +3532,27 @@
         </is>
       </c>
       <c r="D65" s="8" t="n">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>4665743</t>
+          <t>40461849</t>
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
@@ -3234,64 +3560,79 @@
         </is>
       </c>
       <c r="D66" s="8" t="n">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>08589944</t>
+          <t>2739888</t>
         </is>
       </c>
       <c r="B67" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="D67" s="8" t="n">
-        <v>139</v>
+        <v>295</v>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>4443283</t>
+          <t>837888</t>
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="D68" s="8" t="n">
-        <v>438</v>
+        <v>13</v>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>20744666</t>
+          <t>28114888</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
@@ -3299,49 +3640,59 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="D69" s="8" t="n">
-        <v>147</v>
+        <v>52</v>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>下架</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>VIP 3个月</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>382288</t>
+          <t>6611002</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>AABB</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D70" s="8" t="n">
-        <v>55</v>
+        <v>114</v>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>8251353</t>
+          <t>51552166</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
@@ -3349,41 +3700,51 @@
         </is>
       </c>
       <c r="D71" s="8" t="n">
-        <v>125</v>
+        <v>268</v>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>9479999</t>
+          <t>31202169</t>
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>AABB</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D72" s="8" t="n">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>60223569</t>
+          <t>12771670</t>
         </is>
       </c>
       <c r="B73" s="8" t="n">
@@ -3395,18 +3756,23 @@
         </is>
       </c>
       <c r="D73" s="8" t="n">
-        <v>496</v>
+        <v>36</v>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>752500</t>
+          <t>688916</t>
         </is>
       </c>
       <c r="B74" s="8" t="n">
@@ -3418,41 +3784,51 @@
         </is>
       </c>
       <c r="D74" s="8" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>129666</t>
+          <t>99002888</t>
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="D75" s="8" t="n">
-        <v>73</v>
+        <v>205</v>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>058300</t>
+          <t>506633</t>
         </is>
       </c>
       <c r="B76" s="8" t="n">
@@ -3460,72 +3836,87 @@
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>AABB</t>
         </is>
       </c>
       <c r="D76" s="8" t="n">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>1680000</t>
+          <t>85170</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>豹子</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D77" s="8" t="n">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>2570033</t>
+          <t>58837</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>AABB</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D78" s="8" t="n">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>21506</t>
+          <t>689975</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
@@ -3533,45 +3924,55 @@
         </is>
       </c>
       <c r="D79" s="8" t="n">
-        <v>263</v>
+        <v>109</v>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>01001</t>
+          <t>5887722</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>AABB</t>
         </is>
       </c>
       <c r="D80" s="8" t="n">
-        <v>69</v>
+        <v>159</v>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>30461849</t>
+          <t>4163735</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
@@ -3579,11 +3980,16 @@
         </is>
       </c>
       <c r="D81" s="8" t="n">
-        <v>111</v>
+        <v>26</v>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>VIP 6个月</t>
         </is>
       </c>
     </row>
